--- a/research/traditional_assets/database/data/sri_lanka/sri_lanka_bank_money_center.xlsx
+++ b/research/traditional_assets/database/data/sri_lanka/sri_lanka_bank_money_center.xlsx
@@ -588,10 +588,10 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.09039999999999999</v>
+        <v>0.0443</v>
       </c>
       <c r="E2">
-        <v>0.126</v>
+        <v>0.01516</v>
       </c>
       <c r="G2">
         <v>0</v>
@@ -600,91 +600,91 @@
         <v>0</v>
       </c>
       <c r="I2">
-        <v>0.0001301282704296183</v>
+        <v>0.000218935330412409</v>
       </c>
       <c r="J2">
-        <v>9.535062740796522e-05</v>
+        <v>0.0001617942546824641</v>
       </c>
       <c r="K2">
-        <v>408.18</v>
+        <v>180.818</v>
       </c>
       <c r="L2">
-        <v>0.291120462163897</v>
+        <v>0.2337962244634083</v>
       </c>
       <c r="M2">
-        <v>59.346</v>
+        <v>41.9325</v>
       </c>
       <c r="N2">
-        <v>0.03502892220517058</v>
+        <v>0.06957903295390436</v>
       </c>
       <c r="O2">
-        <v>0.1453917389387035</v>
+        <v>0.2319044564147374</v>
       </c>
       <c r="P2">
-        <v>59.346</v>
+        <v>41.7965</v>
       </c>
       <c r="Q2">
-        <v>0.03502892220517058</v>
+        <v>0.06935336674078253</v>
       </c>
       <c r="R2">
-        <v>0.1453917389387035</v>
+        <v>0.2311523189063036</v>
       </c>
       <c r="S2">
-        <v>0</v>
+        <v>0.136</v>
       </c>
       <c r="T2">
-        <v>0</v>
+        <v>0.003243307696893818</v>
       </c>
       <c r="U2">
-        <v>1354.2</v>
+        <v>1199.8</v>
       </c>
       <c r="V2">
-        <v>0.7993153110612679</v>
+        <v>1.990840606643879</v>
       </c>
       <c r="W2">
-        <v>0.1056321005559584</v>
+        <v>0.04210526315789474</v>
       </c>
       <c r="X2">
-        <v>0.2610507805165306</v>
+        <v>0.5197605062720867</v>
       </c>
       <c r="Y2">
-        <v>-0.1554186799605722</v>
+        <v>-0.4776552431141919</v>
       </c>
       <c r="Z2">
-        <v>0.1956510314272113</v>
+        <v>0.1136338862837165</v>
       </c>
       <c r="AA2">
         <v>0</v>
       </c>
       <c r="AB2">
-        <v>0.123086137110535</v>
+        <v>0.228311947950361</v>
       </c>
       <c r="AC2">
-        <v>-0.123086137110535</v>
+        <v>-0.228311947950361</v>
       </c>
       <c r="AD2">
-        <v>4559.3</v>
+        <v>2473</v>
       </c>
       <c r="AE2">
-        <v>0.2027357601531607</v>
+        <v>0.1683770772952145</v>
       </c>
       <c r="AF2">
-        <v>4559.502735760153</v>
+        <v>2473.168377077295</v>
       </c>
       <c r="AG2">
-        <v>3205.302735760153</v>
+        <v>1273.368377077295</v>
       </c>
       <c r="AH2">
-        <v>0.7290884981928925</v>
+        <v>0.8040657910267874</v>
       </c>
       <c r="AI2">
-        <v>0.5549606516049265</v>
+        <v>0.53130790749236</v>
       </c>
       <c r="AJ2">
-        <v>0.6542098063065687</v>
+        <v>0.6787575244789756</v>
       </c>
       <c r="AK2">
-        <v>0.4671293495498626</v>
+        <v>0.3685508470759877</v>
       </c>
       <c r="AL2">
         <v>0</v>
@@ -693,10 +693,10 @@
         <v>0</v>
       </c>
       <c r="AN2">
-        <v>20445.29147982063</v>
+        <v>12182.26600985222</v>
       </c>
       <c r="AP2">
-        <v>14373.55486887961</v>
+        <v>6272.750625996528</v>
       </c>
     </row>
     <row r="3">
@@ -716,10 +716,10 @@
         </is>
       </c>
       <c r="D3">
-        <v>0.115</v>
+        <v>0.114</v>
       </c>
       <c r="E3">
-        <v>0.36</v>
+        <v>0.369</v>
       </c>
       <c r="G3">
         <v>0</v>
@@ -734,10 +734,10 @@
         <v>0</v>
       </c>
       <c r="K3">
-        <v>3.24</v>
+        <v>2.72</v>
       </c>
       <c r="L3">
-        <v>0.1596059113300493</v>
+        <v>0.2158730158730159</v>
       </c>
       <c r="M3">
         <v>-0</v>
@@ -761,55 +761,55 @@
         <v>0</v>
       </c>
       <c r="U3">
-        <v>23.2</v>
+        <v>57.9</v>
       </c>
       <c r="V3">
-        <v>0.3972602739726027</v>
+        <v>2.631818181818182</v>
       </c>
       <c r="W3">
-        <v>0.04901664145234494</v>
+        <v>0.04210526315789474</v>
       </c>
       <c r="X3">
-        <v>0.1176585693561222</v>
+        <v>0.3378667466364795</v>
       </c>
       <c r="Y3">
-        <v>-0.06864192790377721</v>
+        <v>-0.2957614834785848</v>
       </c>
       <c r="Z3">
-        <v>0.9699923547400613</v>
+        <v>0.1855670103092784</v>
       </c>
       <c r="AA3">
         <v>0</v>
       </c>
       <c r="AB3">
-        <v>0.1046446759110529</v>
+        <v>0.2145109732002706</v>
       </c>
       <c r="AC3">
-        <v>-0.1046446759110529</v>
+        <v>-0.2145109732002706</v>
       </c>
       <c r="AD3">
-        <v>26.5</v>
+        <v>44.4</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>26.5</v>
+        <v>44.4</v>
       </c>
       <c r="AG3">
-        <v>3.300000000000001</v>
+        <v>-13.5</v>
       </c>
       <c r="AH3">
-        <v>0.3121319199057715</v>
+        <v>0.6686746987951806</v>
       </c>
       <c r="AI3">
-        <v>0.2908891328210758</v>
+        <v>0.5330132052821128</v>
       </c>
       <c r="AJ3">
-        <v>0.05348460291734199</v>
+        <v>-1.588235294117647</v>
       </c>
       <c r="AK3">
-        <v>0.04860088365243006</v>
+        <v>-0.531496062992126</v>
       </c>
       <c r="AL3">
         <v>0</v>
@@ -826,7 +826,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Union Bank of Colombo PLC (COSE:UBC.N0000)</t>
+          <t>Hatton National Bank PLC (COSE:HNB.N0000)</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -835,10 +835,10 @@
         </is>
       </c>
       <c r="D4">
-        <v>0.0683</v>
+        <v>0.0443</v>
       </c>
       <c r="E4">
-        <v>0.099</v>
+        <v>0.0233</v>
       </c>
       <c r="G4">
         <v>0</v>
@@ -853,28 +853,28 @@
         <v>0</v>
       </c>
       <c r="K4">
-        <v>3.58</v>
+        <v>47.3</v>
       </c>
       <c r="L4">
-        <v>0.1265017667844523</v>
+        <v>0.2436888201957754</v>
       </c>
       <c r="M4">
-        <v>0.705</v>
+        <v>9.33</v>
       </c>
       <c r="N4">
-        <v>0.01188870151770658</v>
+        <v>0.08300711743772242</v>
       </c>
       <c r="O4">
-        <v>0.196927374301676</v>
+        <v>0.1972515856236787</v>
       </c>
       <c r="P4">
-        <v>0.705</v>
+        <v>9.33</v>
       </c>
       <c r="Q4">
-        <v>0.01188870151770658</v>
+        <v>0.08300711743772242</v>
       </c>
       <c r="R4">
-        <v>0.196927374301676</v>
+        <v>0.1972515856236787</v>
       </c>
       <c r="S4">
         <v>0</v>
@@ -883,55 +883,55 @@
         <v>0</v>
       </c>
       <c r="U4">
-        <v>23.8</v>
+        <v>264.6</v>
       </c>
       <c r="V4">
-        <v>0.4013490725126476</v>
+        <v>2.354092526690391</v>
       </c>
       <c r="W4">
-        <v>0.03698347107438017</v>
+        <v>0.05770403806270586</v>
       </c>
       <c r="X4">
-        <v>0.1649544014787416</v>
+        <v>0.3407847738667649</v>
       </c>
       <c r="Y4">
-        <v>-0.1279709304043615</v>
+        <v>-0.2830807358040591</v>
       </c>
       <c r="Z4">
-        <v>0.1493403693931399</v>
+        <v>0.1795891931902295</v>
       </c>
       <c r="AA4">
         <v>0</v>
       </c>
       <c r="AB4">
-        <v>0.1151705839939213</v>
+        <v>0.2167570658256495</v>
       </c>
       <c r="AC4">
-        <v>-0.1151705839939213</v>
+        <v>-0.2167570658256495</v>
       </c>
       <c r="AD4">
-        <v>75.3</v>
+        <v>230.5</v>
       </c>
       <c r="AE4">
         <v>0</v>
       </c>
       <c r="AF4">
-        <v>75.3</v>
+        <v>230.5</v>
       </c>
       <c r="AG4">
-        <v>51.5</v>
+        <v>-34.10000000000002</v>
       </c>
       <c r="AH4">
-        <v>0.5594353640416048</v>
+        <v>0.6722076407115778</v>
       </c>
       <c r="AI4">
-        <v>0.4552599758162032</v>
+        <v>0.3111921155663561</v>
       </c>
       <c r="AJ4">
-        <v>0.4648014440433213</v>
+        <v>-0.435504469987229</v>
       </c>
       <c r="AK4">
-        <v>0.3637005649717514</v>
+        <v>-0.07162360848561232</v>
       </c>
       <c r="AL4">
         <v>0</v>
@@ -948,7 +948,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Sampath Bank PLC (COSE:SAMP.N0000)</t>
+          <t>Seylan Bank PLC (COSE:SEYB.N0000)</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -957,10 +957,10 @@
         </is>
       </c>
       <c r="D5">
-        <v>0.09039999999999999</v>
+        <v>0.0275</v>
       </c>
       <c r="E5">
-        <v>0.0898</v>
+        <v>-0.0304</v>
       </c>
       <c r="G5">
         <v>0</v>
@@ -969,34 +969,34 @@
         <v>0</v>
       </c>
       <c r="I5">
-        <v>0.000790866267747585</v>
+        <v>0</v>
       </c>
       <c r="J5">
-        <v>0.0005704035470922848</v>
+        <v>0</v>
       </c>
       <c r="K5">
-        <v>65.2</v>
+        <v>10.7</v>
       </c>
       <c r="L5">
-        <v>0.282618118768964</v>
+        <v>0.1798319327731092</v>
       </c>
       <c r="M5">
-        <v>15.8</v>
+        <v>0.001</v>
       </c>
       <c r="N5">
-        <v>0.05377808032675289</v>
+        <v>2.155172413793104e-05</v>
       </c>
       <c r="O5">
-        <v>0.2423312883435583</v>
+        <v>9.345794392523365e-05</v>
       </c>
       <c r="P5">
-        <v>15.8</v>
+        <v>0.001</v>
       </c>
       <c r="Q5">
-        <v>0.05377808032675289</v>
+        <v>2.155172413793104e-05</v>
       </c>
       <c r="R5">
-        <v>0.2423312883435583</v>
+        <v>9.345794392523365e-05</v>
       </c>
       <c r="S5">
         <v>0</v>
@@ -1005,67 +1005,61 @@
         <v>0</v>
       </c>
       <c r="U5">
-        <v>118.6</v>
+        <v>94.7</v>
       </c>
       <c r="V5">
-        <v>0.4036759700476514</v>
+        <v>2.040948275862069</v>
       </c>
       <c r="W5">
-        <v>0.1077685950413223</v>
+        <v>0.04076190476190476</v>
       </c>
       <c r="X5">
-        <v>0.182833005375755</v>
+        <v>0.4680835178999435</v>
       </c>
       <c r="Y5">
-        <v>-0.07506441033443266</v>
+        <v>-0.4273216131380387</v>
       </c>
       <c r="Z5">
-        <v>0.2168635144890378</v>
+        <v>0.1221013749230454</v>
       </c>
       <c r="AA5">
-        <v>0.0001236997178994463</v>
+        <v>0</v>
       </c>
       <c r="AB5">
-        <v>0.11741411839918</v>
+        <v>0.2192501970721273</v>
       </c>
       <c r="AC5">
-        <v>-0.1172904186812805</v>
+        <v>-0.2192501970721273</v>
       </c>
       <c r="AD5">
-        <v>463.5</v>
+        <v>161</v>
       </c>
       <c r="AE5">
-        <v>0.2027357601531607</v>
+        <v>0</v>
       </c>
       <c r="AF5">
-        <v>463.7027357601532</v>
+        <v>161</v>
       </c>
       <c r="AG5">
-        <v>345.1027357601532</v>
+        <v>66.3</v>
       </c>
       <c r="AH5">
-        <v>0.6121466152789904</v>
+        <v>0.7762777242044359</v>
       </c>
       <c r="AI5">
-        <v>0.4314706944820135</v>
+        <v>0.5119236883942766</v>
       </c>
       <c r="AJ5">
-        <v>0.5401490969506604</v>
+        <v>0.5882874889086069</v>
       </c>
       <c r="AK5">
-        <v>0.3609473363610637</v>
+        <v>0.3016378525932666</v>
       </c>
       <c r="AL5">
         <v>0</v>
       </c>
       <c r="AM5">
         <v>0</v>
-      </c>
-      <c r="AN5">
-        <v>2078.47533632287</v>
-      </c>
-      <c r="AP5">
-        <v>1547.545900269745</v>
       </c>
     </row>
     <row r="6">
@@ -1076,7 +1070,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Hatton National Bank PLC (COSE:HNB.N0000)</t>
+          <t>Union Bank of Colombo PLC (COSE:UBC.N0000)</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1085,10 +1079,10 @@
         </is>
       </c>
       <c r="D6">
-        <v>0.0489</v>
+        <v>0.0451</v>
       </c>
       <c r="E6">
-        <v>0.0415</v>
+        <v>-0.0136</v>
       </c>
       <c r="G6">
         <v>0</v>
@@ -1103,85 +1097,82 @@
         <v>0</v>
       </c>
       <c r="K6">
-        <v>87.40000000000001</v>
+        <v>1.33</v>
       </c>
       <c r="L6">
-        <v>0.271597265382225</v>
+        <v>0.08209876543209878</v>
       </c>
       <c r="M6">
-        <v>11.4</v>
+        <v>-0</v>
       </c>
       <c r="N6">
-        <v>0.03320710748616371</v>
+        <v>-0</v>
       </c>
       <c r="O6">
-        <v>0.1304347826086956</v>
+        <v>-0</v>
       </c>
       <c r="P6">
-        <v>11.4</v>
+        <v>-0</v>
       </c>
       <c r="Q6">
-        <v>0.03320710748616371</v>
+        <v>-0</v>
       </c>
       <c r="R6">
-        <v>0.1304347826086956</v>
+        <v>-0</v>
       </c>
       <c r="S6">
         <v>0</v>
       </c>
-      <c r="T6">
-        <v>0</v>
-      </c>
       <c r="U6">
-        <v>341.7</v>
+        <v>16.3</v>
       </c>
       <c r="V6">
-        <v>0.9953393533352752</v>
+        <v>0.8358974358974359</v>
       </c>
       <c r="W6">
-        <v>0.1056321005559584</v>
+        <v>0.01496062992125984</v>
       </c>
       <c r="X6">
-        <v>0.1931264830506435</v>
+        <v>0.4250186123067822</v>
       </c>
       <c r="Y6">
-        <v>-0.08749438249468504</v>
+        <v>-0.4100579823855224</v>
       </c>
       <c r="Z6">
-        <v>0.2140481575096448</v>
+        <v>0.1153846153846154</v>
       </c>
       <c r="AA6">
         <v>0</v>
       </c>
       <c r="AB6">
-        <v>0.1184779879663306</v>
+        <v>0.2214707797408157</v>
       </c>
       <c r="AC6">
-        <v>-0.1184779879663306</v>
+        <v>-0.2214707797408157</v>
       </c>
       <c r="AD6">
-        <v>602.8</v>
+        <v>58.3</v>
       </c>
       <c r="AE6">
         <v>0</v>
       </c>
       <c r="AF6">
-        <v>602.8</v>
+        <v>58.3</v>
       </c>
       <c r="AG6">
-        <v>261.1</v>
+        <v>42</v>
       </c>
       <c r="AH6">
-        <v>0.6371419511679527</v>
+        <v>0.7493573264781491</v>
       </c>
       <c r="AI6">
-        <v>0.4154948993658671</v>
+        <v>0.5295186194368756</v>
       </c>
       <c r="AJ6">
-        <v>0.4319986763732627</v>
+        <v>0.6829268292682927</v>
       </c>
       <c r="AK6">
-        <v>0.2354161031466955</v>
+        <v>0.4477611940298508</v>
       </c>
       <c r="AL6">
         <v>0</v>
@@ -1198,7 +1189,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Pan Asia Banking Corporation PLC (COSE:PABC.N0000)</t>
+          <t>Sampath Bank PLC (COSE:SAMP.N0000)</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1207,10 +1198,10 @@
         </is>
       </c>
       <c r="D7">
-        <v>0.09089999999999999</v>
+        <v>0.0433</v>
       </c>
       <c r="E7">
-        <v>0.186</v>
+        <v>0.007019999999999999</v>
       </c>
       <c r="G7">
         <v>0</v>
@@ -1219,94 +1210,103 @@
         <v>0</v>
       </c>
       <c r="I7">
-        <v>0</v>
+        <v>0.001320784590803098</v>
       </c>
       <c r="J7">
-        <v>0</v>
+        <v>0.0009983395263816843</v>
       </c>
       <c r="K7">
-        <v>14</v>
+        <v>32.2</v>
       </c>
       <c r="L7">
-        <v>0.3131991051454138</v>
+        <v>0.2511700468018721</v>
       </c>
       <c r="M7">
-        <v>-0</v>
+        <v>13.3</v>
       </c>
       <c r="N7">
-        <v>-0</v>
+        <v>0.1248826291079812</v>
       </c>
       <c r="O7">
-        <v>-0</v>
+        <v>0.4130434782608696</v>
       </c>
       <c r="P7">
-        <v>-0</v>
+        <v>13.3</v>
       </c>
       <c r="Q7">
-        <v>-0</v>
+        <v>0.1248826291079812</v>
       </c>
       <c r="R7">
-        <v>-0</v>
+        <v>0.4130434782608696</v>
       </c>
       <c r="S7">
         <v>0</v>
       </c>
+      <c r="T7">
+        <v>0</v>
+      </c>
       <c r="U7">
-        <v>13</v>
+        <v>135.6</v>
       </c>
       <c r="V7">
-        <v>0.3846153846153846</v>
+        <v>1.273239436619718</v>
       </c>
       <c r="W7">
-        <v>0.1772151898734177</v>
+        <v>0.05270049099836335</v>
       </c>
       <c r="X7">
-        <v>0.2293936830811563</v>
+        <v>0.4035073492462563</v>
       </c>
       <c r="Y7">
-        <v>-0.0521784932077386</v>
+        <v>-0.3508068582478929</v>
       </c>
       <c r="Z7">
-        <v>0.2966157929661579</v>
+        <v>0.1340908276789866</v>
       </c>
       <c r="AA7">
-        <v>0</v>
+        <v>0.0001338681733971675</v>
       </c>
       <c r="AB7">
-        <v>0.1213358625791398</v>
+        <v>0.2222059980723402</v>
       </c>
       <c r="AC7">
-        <v>-0.1213358625791398</v>
+        <v>-0.222072129898943</v>
       </c>
       <c r="AD7">
-        <v>80.5</v>
+        <v>292.7</v>
       </c>
       <c r="AE7">
-        <v>0</v>
+        <v>0.1683770772952145</v>
       </c>
       <c r="AF7">
-        <v>80.5</v>
+        <v>292.8683770772952</v>
       </c>
       <c r="AG7">
-        <v>67.5</v>
+        <v>157.2683770772952</v>
       </c>
       <c r="AH7">
-        <v>0.7042869641294839</v>
+        <v>0.7333289110685206</v>
       </c>
       <c r="AI7">
-        <v>0.4794520547945205</v>
+        <v>0.4556359452669165</v>
       </c>
       <c r="AJ7">
-        <v>0.6663376110562685</v>
+        <v>0.5962366634693625</v>
       </c>
       <c r="AK7">
-        <v>0.4357650096836669</v>
+        <v>0.3100910549344575</v>
       </c>
       <c r="AL7">
         <v>0</v>
       </c>
       <c r="AM7">
         <v>0</v>
+      </c>
+      <c r="AN7">
+        <v>1441.871921182266</v>
+      </c>
+      <c r="AP7">
+        <v>774.7210693462816</v>
       </c>
     </row>
     <row r="8">
@@ -1317,7 +1317,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Seylan Bank PLC (COSE:SEYB.N0000)</t>
+          <t>Nations Trust Bank PLC (COSE:NTB.N0000)</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1326,10 +1326,10 @@
         </is>
       </c>
       <c r="D8">
-        <v>0.0472</v>
+        <v>0.0898</v>
       </c>
       <c r="E8">
-        <v>0.00621</v>
+        <v>0.163</v>
       </c>
       <c r="G8">
         <v>0</v>
@@ -1344,28 +1344,28 @@
         <v>0</v>
       </c>
       <c r="K8">
-        <v>20.4</v>
+        <v>19.1</v>
       </c>
       <c r="L8">
-        <v>0.1952153110047847</v>
+        <v>0.305111821086262</v>
       </c>
       <c r="M8">
-        <v>0.003</v>
+        <v>2.7135</v>
       </c>
       <c r="N8">
-        <v>2.671415850400713e-05</v>
+        <v>0.06922193877551019</v>
       </c>
       <c r="O8">
-        <v>0.0001470588235294118</v>
+        <v>0.1420680628272251</v>
       </c>
       <c r="P8">
-        <v>0.003</v>
+        <v>2.7135</v>
       </c>
       <c r="Q8">
-        <v>2.671415850400713e-05</v>
+        <v>0.06922193877551019</v>
       </c>
       <c r="R8">
-        <v>0.0001470588235294118</v>
+        <v>0.1420680628272251</v>
       </c>
       <c r="S8">
         <v>0</v>
@@ -1374,55 +1374,55 @@
         <v>0</v>
       </c>
       <c r="U8">
-        <v>104</v>
+        <v>139</v>
       </c>
       <c r="V8">
-        <v>0.9260908281389136</v>
+        <v>3.545918367346939</v>
       </c>
       <c r="W8">
-        <v>0.07396664249456127</v>
+        <v>0.09891248058001037</v>
       </c>
       <c r="X8">
-        <v>0.2610507805165306</v>
+        <v>0.5197605062720867</v>
       </c>
       <c r="Y8">
-        <v>-0.1870841380219694</v>
+        <v>-0.4208480256920764</v>
       </c>
       <c r="Z8">
-        <v>0.2379326047358834</v>
+        <v>0.1408640864086408</v>
       </c>
       <c r="AA8">
         <v>0</v>
       </c>
       <c r="AB8">
-        <v>0.123086137110535</v>
+        <v>0.228311947950361</v>
       </c>
       <c r="AC8">
-        <v>-0.123086137110535</v>
+        <v>-0.228311947950361</v>
       </c>
       <c r="AD8">
-        <v>328.8</v>
+        <v>158.6</v>
       </c>
       <c r="AE8">
         <v>0</v>
       </c>
       <c r="AF8">
-        <v>328.8</v>
+        <v>158.6</v>
       </c>
       <c r="AG8">
-        <v>224.8</v>
+        <v>19.59999999999999</v>
       </c>
       <c r="AH8">
-        <v>0.7454092042620721</v>
+        <v>0.8018200202224468</v>
       </c>
       <c r="AI8">
-        <v>0.5500167280026765</v>
+        <v>0.5700934579439252</v>
       </c>
       <c r="AJ8">
-        <v>0.6668644319193118</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="AK8">
-        <v>0.4552450384771163</v>
+        <v>0.1408045977011494</v>
       </c>
       <c r="AL8">
         <v>0</v>
@@ -1439,7 +1439,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Commercial Bank of Ceylon PLC (COSE:COMB.N0000)</t>
+          <t>Pan Asia Banking Corporation PLC (COSE:PABC.N0000)</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1448,10 +1448,10 @@
         </is>
       </c>
       <c r="D9">
-        <v>0.104</v>
+        <v>0.0341</v>
       </c>
       <c r="E9">
-        <v>0.126</v>
+        <v>0.0349</v>
       </c>
       <c r="G9">
         <v>0</v>
@@ -1466,85 +1466,82 @@
         <v>0</v>
       </c>
       <c r="K9">
-        <v>123.7</v>
+        <v>4.11</v>
       </c>
       <c r="L9">
-        <v>0.367935752528257</v>
+        <v>0.2118556701030928</v>
       </c>
       <c r="M9">
-        <v>25.9</v>
+        <v>-0</v>
       </c>
       <c r="N9">
-        <v>0.05579491598448944</v>
+        <v>-0</v>
       </c>
       <c r="O9">
-        <v>0.2093775262732417</v>
+        <v>-0</v>
       </c>
       <c r="P9">
-        <v>25.9</v>
+        <v>-0</v>
       </c>
       <c r="Q9">
-        <v>0.05579491598448944</v>
+        <v>-0</v>
       </c>
       <c r="R9">
-        <v>0.2093775262732417</v>
+        <v>-0</v>
       </c>
       <c r="S9">
         <v>0</v>
       </c>
-      <c r="T9">
-        <v>0</v>
-      </c>
       <c r="U9">
-        <v>465.5</v>
+        <v>18.5</v>
       </c>
       <c r="V9">
-        <v>1.002800517018527</v>
+        <v>1.62280701754386</v>
       </c>
       <c r="W9">
-        <v>0.1587525667351129</v>
+        <v>0.04702517162471396</v>
       </c>
       <c r="X9">
-        <v>0.2823735818619403</v>
+        <v>0.6171473609251668</v>
       </c>
       <c r="Y9">
-        <v>-0.1236210151268274</v>
+        <v>-0.5701221893004528</v>
       </c>
       <c r="Z9">
-        <v>0.1770965023177412</v>
+        <v>0.1252420916720465</v>
       </c>
       <c r="AA9">
         <v>0</v>
       </c>
       <c r="AB9">
-        <v>0.1240141779194785</v>
+        <v>0.2290231958086404</v>
       </c>
       <c r="AC9">
-        <v>-0.1240141779194785</v>
+        <v>-0.2290231958086404</v>
       </c>
       <c r="AD9">
-        <v>1529.9</v>
+        <v>58.5</v>
       </c>
       <c r="AE9">
         <v>0</v>
       </c>
       <c r="AF9">
-        <v>1529.9</v>
+        <v>58.5</v>
       </c>
       <c r="AG9">
-        <v>1064.4</v>
+        <v>40</v>
       </c>
       <c r="AH9">
-        <v>0.767213279173562</v>
+        <v>0.8369098712446351</v>
       </c>
       <c r="AI9">
-        <v>0.645364042858348</v>
+        <v>0.5294117647058824</v>
       </c>
       <c r="AJ9">
-        <v>0.696323433206856</v>
+        <v>0.7782101167315175</v>
       </c>
       <c r="AK9">
-        <v>0.558710828827883</v>
+        <v>0.4347826086956522</v>
       </c>
       <c r="AL9">
         <v>0</v>
@@ -1561,7 +1558,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>National Development Bank PLC (COSE:NDB.N0000)</t>
+          <t>Commercial Bank of Ceylon PLC (COSE:COMB.N0000)</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1570,10 +1567,10 @@
         </is>
       </c>
       <c r="D10">
-        <v>0.127</v>
+        <v>0.079</v>
       </c>
       <c r="E10">
-        <v>0.175</v>
+        <v>0.0473</v>
       </c>
       <c r="G10">
         <v>0</v>
@@ -1588,28 +1585,28 @@
         <v>0</v>
       </c>
       <c r="K10">
-        <v>36.1</v>
+        <v>55.5</v>
       </c>
       <c r="L10">
-        <v>0.3228980322003578</v>
+        <v>0.293495505023797</v>
       </c>
       <c r="M10">
-        <v>1.67</v>
+        <v>14.6</v>
       </c>
       <c r="N10">
-        <v>0.01376751854905194</v>
+        <v>0.08706022659511033</v>
       </c>
       <c r="O10">
-        <v>0.04626038781163434</v>
+        <v>0.263063063063063</v>
       </c>
       <c r="P10">
-        <v>1.67</v>
+        <v>14.6</v>
       </c>
       <c r="Q10">
-        <v>0.01376751854905194</v>
+        <v>0.08706022659511033</v>
       </c>
       <c r="R10">
-        <v>0.04626038781163434</v>
+        <v>0.263063063063063</v>
       </c>
       <c r="S10">
         <v>0</v>
@@ -1618,55 +1615,55 @@
         <v>0</v>
       </c>
       <c r="U10">
-        <v>77.3</v>
+        <v>320.9</v>
       </c>
       <c r="V10">
-        <v>0.6372629843363561</v>
+        <v>1.913536076326774</v>
       </c>
       <c r="W10">
-        <v>0.1429136975455265</v>
+        <v>0.06682721252257676</v>
       </c>
       <c r="X10">
-        <v>0.2938036078157025</v>
+        <v>0.5535659608408841</v>
       </c>
       <c r="Y10">
-        <v>-0.1508899102701759</v>
+        <v>-0.4867387483183073</v>
       </c>
       <c r="Z10">
-        <v>0.1825008161932745</v>
+        <v>0.09979418438967755</v>
       </c>
       <c r="AA10">
         <v>0</v>
       </c>
       <c r="AB10">
-        <v>0.1244490801447126</v>
+        <v>0.2295397756813018</v>
       </c>
       <c r="AC10">
-        <v>-0.1244490801447126</v>
+        <v>-0.2295397756813018</v>
       </c>
       <c r="AD10">
-        <v>423.7</v>
+        <v>741.7</v>
       </c>
       <c r="AE10">
         <v>0</v>
       </c>
       <c r="AF10">
-        <v>423.7</v>
+        <v>741.7</v>
       </c>
       <c r="AG10">
-        <v>346.4</v>
+        <v>420.8000000000001</v>
       </c>
       <c r="AH10">
-        <v>0.7774311926605504</v>
+        <v>0.8155926984825159</v>
       </c>
       <c r="AI10">
-        <v>0.5727223573938902</v>
+        <v>0.5700561063715318</v>
       </c>
       <c r="AJ10">
-        <v>0.7406457130639298</v>
+        <v>0.7150382327952423</v>
       </c>
       <c r="AK10">
-        <v>0.5228679245283019</v>
+        <v>0.4293001428279943</v>
       </c>
       <c r="AL10">
         <v>0</v>
@@ -1683,7 +1680,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Nations Trust Bank PLC (COSE:NTB.N0000)</t>
+          <t>DFCC Bank PLC (COSE:DFCC.N0000)</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1692,10 +1689,10 @@
         </is>
       </c>
       <c r="D11">
-        <v>0.08839999999999999</v>
+        <v>-0.00511</v>
       </c>
       <c r="E11">
-        <v>0.171</v>
+        <v>-0.189</v>
       </c>
       <c r="G11">
         <v>0</v>
@@ -1710,28 +1707,28 @@
         <v>0</v>
       </c>
       <c r="K11">
-        <v>29.8</v>
+        <v>3.93</v>
       </c>
       <c r="L11">
-        <v>0.3104166666666667</v>
+        <v>0.1126074498567335</v>
       </c>
       <c r="M11">
-        <v>2.74</v>
+        <v>0.245</v>
       </c>
       <c r="N11">
-        <v>0.03472750316856781</v>
+        <v>0.006980056980056979</v>
       </c>
       <c r="O11">
-        <v>0.09194630872483223</v>
+        <v>0.06234096692111959</v>
       </c>
       <c r="P11">
-        <v>2.74</v>
+        <v>0.245</v>
       </c>
       <c r="Q11">
-        <v>0.03472750316856781</v>
+        <v>0.006980056980056979</v>
       </c>
       <c r="R11">
-        <v>0.09194630872483223</v>
+        <v>0.06234096692111959</v>
       </c>
       <c r="S11">
         <v>0</v>
@@ -1740,55 +1737,55 @@
         <v>0</v>
       </c>
       <c r="U11">
-        <v>86.2</v>
+        <v>51.6</v>
       </c>
       <c r="V11">
-        <v>1.092522179974651</v>
+        <v>1.47008547008547</v>
       </c>
       <c r="W11">
-        <v>0.1569246972090574</v>
+        <v>0.0148694665153235</v>
       </c>
       <c r="X11">
-        <v>0.3400833502226575</v>
+        <v>1.091682059913699</v>
       </c>
       <c r="Y11">
-        <v>-0.1831586530136001</v>
+        <v>-1.076812593398375</v>
       </c>
       <c r="Z11">
-        <v>0.2194285714285714</v>
+        <v>0.04825774336283185</v>
       </c>
       <c r="AA11">
         <v>0</v>
       </c>
       <c r="AB11">
-        <v>0.1258786246054098</v>
+        <v>0.2301995034572172</v>
       </c>
       <c r="AC11">
-        <v>-0.1258786246054098</v>
+        <v>-0.2301995034572172</v>
       </c>
       <c r="AD11">
-        <v>338.6</v>
+        <v>365.8</v>
       </c>
       <c r="AE11">
         <v>0</v>
       </c>
       <c r="AF11">
-        <v>338.6</v>
+        <v>365.8</v>
       </c>
       <c r="AG11">
-        <v>252.4</v>
+        <v>314.2</v>
       </c>
       <c r="AH11">
-        <v>0.8110179640718563</v>
+        <v>0.9124469942629084</v>
       </c>
       <c r="AI11">
-        <v>0.6368252774120745</v>
+        <v>0.7418373555059825</v>
       </c>
       <c r="AJ11">
-        <v>0.7618472683368548</v>
+        <v>0.8995133123389636</v>
       </c>
       <c r="AK11">
-        <v>0.5665544332211</v>
+        <v>0.7116647791619479</v>
       </c>
       <c r="AL11">
         <v>0</v>
@@ -1805,7 +1802,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>DFCC Bank PLC (COSE:DFCC.N0000)</t>
+          <t>National Development Bank PLC (COSE:NDB.N0000)</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1814,10 +1811,10 @@
         </is>
       </c>
       <c r="D12">
-        <v>0.0572</v>
+        <v>0.00971</v>
       </c>
       <c r="E12">
-        <v>0.0548</v>
+        <v>-0.134</v>
       </c>
       <c r="G12">
         <v>0</v>
@@ -1832,28 +1829,28 @@
         <v>0</v>
       </c>
       <c r="K12">
-        <v>20.2</v>
+        <v>4.32</v>
       </c>
       <c r="L12">
-        <v>0.2759562841530054</v>
+        <v>0.1046004842615012</v>
       </c>
       <c r="M12">
-        <v>0.098</v>
+        <v>0.947</v>
       </c>
       <c r="N12">
-        <v>0.001033755274261603</v>
+        <v>0.02861027190332326</v>
       </c>
       <c r="O12">
-        <v>0.004851485148514851</v>
+        <v>0.2192129629629629</v>
       </c>
       <c r="P12">
-        <v>0.098</v>
+        <v>0.947</v>
       </c>
       <c r="Q12">
-        <v>0.001033755274261603</v>
+        <v>0.02861027190332326</v>
       </c>
       <c r="R12">
-        <v>0.004851485148514851</v>
+        <v>0.2192129629629629</v>
       </c>
       <c r="S12">
         <v>0</v>
@@ -1862,55 +1859,55 @@
         <v>0</v>
       </c>
       <c r="U12">
-        <v>47.3</v>
+        <v>81.59999999999999</v>
       </c>
       <c r="V12">
-        <v>0.4989451476793249</v>
+        <v>2.465256797583081</v>
       </c>
       <c r="W12">
-        <v>0.07340116279069768</v>
+        <v>0.01394898288666451</v>
       </c>
       <c r="X12">
-        <v>0.4008314474135867</v>
+        <v>0.855482528996665</v>
       </c>
       <c r="Y12">
-        <v>-0.327430284622889</v>
+        <v>-0.8415335461100005</v>
       </c>
       <c r="Z12">
-        <v>0.1000820344544709</v>
+        <v>0.06294772138393537</v>
       </c>
       <c r="AA12">
         <v>0</v>
       </c>
       <c r="AB12">
-        <v>0.1272084939648658</v>
+        <v>0.2358357376622084</v>
       </c>
       <c r="AC12">
-        <v>-0.1272084939648658</v>
+        <v>-0.2358357376622084</v>
       </c>
       <c r="AD12">
-        <v>506.2</v>
+        <v>257.8</v>
       </c>
       <c r="AE12">
         <v>0</v>
       </c>
       <c r="AF12">
-        <v>506.2</v>
+        <v>257.8</v>
       </c>
       <c r="AG12">
-        <v>458.9</v>
+        <v>176.2</v>
       </c>
       <c r="AH12">
-        <v>0.8422628951747088</v>
+        <v>0.8862151942248194</v>
       </c>
       <c r="AI12">
-        <v>0.6553599171413775</v>
+        <v>0.5844479709816368</v>
       </c>
       <c r="AJ12">
-        <v>0.8287881524291133</v>
+        <v>0.8418537983755375</v>
       </c>
       <c r="AK12">
-        <v>0.6328782236932837</v>
+        <v>0.4901251738525731</v>
       </c>
       <c r="AL12">
         <v>0</v>
@@ -1936,10 +1933,7 @@
         </is>
       </c>
       <c r="D13">
-        <v>0.147</v>
-      </c>
-      <c r="E13">
-        <v>0.187</v>
+        <v>0.0751</v>
       </c>
       <c r="G13">
         <v>0</v>
@@ -1954,85 +1948,85 @@
         <v>0</v>
       </c>
       <c r="K13">
-        <v>4.56</v>
+        <v>-0.392</v>
       </c>
       <c r="L13">
-        <v>0.1317919075144509</v>
+        <v>-0.02529032258064516</v>
       </c>
       <c r="M13">
-        <v>1.03</v>
+        <v>0.796</v>
       </c>
       <c r="N13">
-        <v>0.03020527859237537</v>
+        <v>0.08504273504273505</v>
       </c>
       <c r="O13">
-        <v>0.2258771929824562</v>
+        <v>-2.030612244897959</v>
       </c>
       <c r="P13">
-        <v>1.03</v>
+        <v>0.66</v>
       </c>
       <c r="Q13">
-        <v>0.03020527859237537</v>
+        <v>0.07051282051282053</v>
       </c>
       <c r="R13">
-        <v>0.2258771929824562</v>
+        <v>-1.683673469387755</v>
       </c>
       <c r="S13">
-        <v>0</v>
+        <v>0.136</v>
       </c>
       <c r="T13">
-        <v>0</v>
+        <v>0.1708542713567839</v>
       </c>
       <c r="U13">
-        <v>53.6</v>
+        <v>19.1</v>
       </c>
       <c r="V13">
-        <v>1.571847507331378</v>
+        <v>2.040598290598291</v>
       </c>
       <c r="W13">
-        <v>0.1034013605442177</v>
+        <v>-0.005584045584045584</v>
       </c>
       <c r="X13">
-        <v>0.4032406838180205</v>
+        <v>1.150653381900702</v>
       </c>
       <c r="Y13">
-        <v>-0.2998393232738029</v>
+        <v>-1.156237427484748</v>
       </c>
       <c r="Z13">
-        <v>0.2910008410428932</v>
+        <v>0.07746126936531735</v>
       </c>
       <c r="AA13">
         <v>0</v>
       </c>
       <c r="AB13">
-        <v>0.1272522291210957</v>
+        <v>0.2359501885375771</v>
       </c>
       <c r="AC13">
-        <v>-0.1272522291210957</v>
+        <v>-0.2359501885375771</v>
       </c>
       <c r="AD13">
-        <v>183.5</v>
+        <v>103.7</v>
       </c>
       <c r="AE13">
         <v>0</v>
       </c>
       <c r="AF13">
-        <v>183.5</v>
+        <v>103.7</v>
       </c>
       <c r="AG13">
-        <v>129.9</v>
+        <v>84.59999999999999</v>
       </c>
       <c r="AH13">
-        <v>0.8432904411764706</v>
+        <v>0.9172120997700336</v>
       </c>
       <c r="AI13">
-        <v>0.7232952305873078</v>
+        <v>0.7433691756272401</v>
       </c>
       <c r="AJ13">
-        <v>0.7920731707317074</v>
+        <v>0.9003831417624522</v>
       </c>
       <c r="AK13">
-        <v>0.649175412293853</v>
+        <v>0.7026578073089701</v>
       </c>
       <c r="AL13">
         <v>0</v>

--- a/research/traditional_assets/database/data/sri_lanka/sri_lanka_bank_money_center.xlsx
+++ b/research/traditional_assets/database/data/sri_lanka/sri_lanka_bank_money_center.xlsx
@@ -588,10 +588,10 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.0443</v>
+        <v>0.0922</v>
       </c>
       <c r="E2">
-        <v>0.01516</v>
+        <v>0.101</v>
       </c>
       <c r="G2">
         <v>0</v>
@@ -600,91 +600,91 @@
         <v>0</v>
       </c>
       <c r="I2">
-        <v>0.000218935330412409</v>
+        <v>0.0001202328011446177</v>
       </c>
       <c r="J2">
-        <v>0.0001617942546824641</v>
+        <v>9.10778412498108e-05</v>
       </c>
       <c r="K2">
-        <v>180.818</v>
+        <v>322.33</v>
       </c>
       <c r="L2">
-        <v>0.2337962244634083</v>
+        <v>0.2664544928494668</v>
       </c>
       <c r="M2">
-        <v>41.9325</v>
+        <v>30.6043</v>
       </c>
       <c r="N2">
-        <v>0.06957903295390436</v>
+        <v>0.02215455335167222</v>
       </c>
       <c r="O2">
-        <v>0.2319044564147374</v>
+        <v>0.09494710389973009</v>
       </c>
       <c r="P2">
-        <v>41.7965</v>
+        <v>30.6043</v>
       </c>
       <c r="Q2">
-        <v>0.06935336674078253</v>
+        <v>0.02215455335167222</v>
       </c>
       <c r="R2">
-        <v>0.2311523189063036</v>
+        <v>0.09494710389973009</v>
       </c>
       <c r="S2">
-        <v>0.136</v>
+        <v>0</v>
       </c>
       <c r="T2">
-        <v>0.003243307696893818</v>
+        <v>0</v>
       </c>
       <c r="U2">
-        <v>1199.8</v>
+        <v>1938.97</v>
       </c>
       <c r="V2">
-        <v>1.990840606643879</v>
+        <v>1.40362675546547</v>
       </c>
       <c r="W2">
-        <v>0.04210526315789474</v>
+        <v>0.1354236157438292</v>
       </c>
       <c r="X2">
-        <v>0.5197605062720867</v>
+        <v>0.2603034111009942</v>
       </c>
       <c r="Y2">
-        <v>-0.4776552431141919</v>
+        <v>-0.124879795357165</v>
       </c>
       <c r="Z2">
-        <v>0.1136338862837165</v>
+        <v>0.3540501321016443</v>
       </c>
       <c r="AA2">
         <v>0</v>
       </c>
       <c r="AB2">
-        <v>0.228311947950361</v>
+        <v>0.1797691720194247</v>
       </c>
       <c r="AC2">
-        <v>-0.228311947950361</v>
+        <v>-0.1797691720194247</v>
       </c>
       <c r="AD2">
-        <v>2473</v>
+        <v>2407.35</v>
       </c>
       <c r="AE2">
-        <v>0.1683770772952145</v>
+        <v>0.14777190227678</v>
       </c>
       <c r="AF2">
-        <v>2473.168377077295</v>
+        <v>2407.497771902277</v>
       </c>
       <c r="AG2">
-        <v>1273.368377077295</v>
+        <v>468.5277719022768</v>
       </c>
       <c r="AH2">
-        <v>0.8040657910267874</v>
+        <v>0.635408479414728</v>
       </c>
       <c r="AI2">
-        <v>0.53130790749236</v>
+        <v>0.4563200190731197</v>
       </c>
       <c r="AJ2">
-        <v>0.6787575244789756</v>
+        <v>0.2532681432316088</v>
       </c>
       <c r="AK2">
-        <v>0.3685508470759877</v>
+        <v>0.1404069263492581</v>
       </c>
       <c r="AL2">
         <v>0</v>
@@ -693,10 +693,10 @@
         <v>0</v>
       </c>
       <c r="AN2">
-        <v>12182.26600985222</v>
+        <v>13756.28571428571</v>
       </c>
       <c r="AP2">
-        <v>6272.750625996528</v>
+        <v>2677.301553727296</v>
       </c>
     </row>
     <row r="3">
@@ -716,10 +716,10 @@
         </is>
       </c>
       <c r="D3">
-        <v>0.114</v>
+        <v>0.132</v>
       </c>
       <c r="E3">
-        <v>0.369</v>
+        <v>0.101</v>
       </c>
       <c r="G3">
         <v>0</v>
@@ -734,10 +734,10 @@
         <v>0</v>
       </c>
       <c r="K3">
-        <v>2.72</v>
+        <v>3.34</v>
       </c>
       <c r="L3">
-        <v>0.2158730158730159</v>
+        <v>0.1653465346534654</v>
       </c>
       <c r="M3">
         <v>-0</v>
@@ -761,55 +761,55 @@
         <v>0</v>
       </c>
       <c r="U3">
-        <v>57.9</v>
+        <v>40.2</v>
       </c>
       <c r="V3">
-        <v>2.631818181818182</v>
+        <v>1.951456310679612</v>
       </c>
       <c r="W3">
-        <v>0.04210526315789474</v>
+        <v>0.08586118251928021</v>
       </c>
       <c r="X3">
-        <v>0.3378667466364795</v>
+        <v>0.1306560554056599</v>
       </c>
       <c r="Y3">
-        <v>-0.2957614834785848</v>
+        <v>-0.04479487288637965</v>
       </c>
       <c r="Z3">
-        <v>0.1855670103092784</v>
+        <v>0.7952755905511811</v>
       </c>
       <c r="AA3">
         <v>0</v>
       </c>
       <c r="AB3">
-        <v>0.2145109732002706</v>
+        <v>0.1311394735126005</v>
       </c>
       <c r="AC3">
-        <v>-0.2145109732002706</v>
+        <v>-0.1311394735126005</v>
       </c>
       <c r="AD3">
-        <v>44.4</v>
+        <v>1.45</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>44.4</v>
+        <v>1.45</v>
       </c>
       <c r="AG3">
-        <v>-13.5</v>
+        <v>-38.75</v>
       </c>
       <c r="AH3">
-        <v>0.6686746987951806</v>
+        <v>0.06575963718820861</v>
       </c>
       <c r="AI3">
-        <v>0.5330132052821128</v>
+        <v>0.02986611740473738</v>
       </c>
       <c r="AJ3">
-        <v>-1.588235294117647</v>
+        <v>2.134986225895317</v>
       </c>
       <c r="AK3">
-        <v>-0.531496062992126</v>
+        <v>-4.640718562874251</v>
       </c>
       <c r="AL3">
         <v>0</v>
@@ -835,10 +835,10 @@
         </is>
       </c>
       <c r="D4">
-        <v>0.0443</v>
+        <v>0.08749999999999999</v>
       </c>
       <c r="E4">
-        <v>0.0233</v>
+        <v>0.0545</v>
       </c>
       <c r="G4">
         <v>0</v>
@@ -853,28 +853,28 @@
         <v>0</v>
       </c>
       <c r="K4">
-        <v>47.3</v>
+        <v>70.09999999999999</v>
       </c>
       <c r="L4">
-        <v>0.2436888201957754</v>
+        <v>0.2365845426932163</v>
       </c>
       <c r="M4">
-        <v>9.33</v>
+        <v>0.064</v>
       </c>
       <c r="N4">
-        <v>0.08300711743772242</v>
+        <v>0.0002263883975946233</v>
       </c>
       <c r="O4">
-        <v>0.1972515856236787</v>
+        <v>0.0009129814550641941</v>
       </c>
       <c r="P4">
-        <v>9.33</v>
+        <v>0.064</v>
       </c>
       <c r="Q4">
-        <v>0.08300711743772242</v>
+        <v>0.0002263883975946233</v>
       </c>
       <c r="R4">
-        <v>0.1972515856236787</v>
+        <v>0.0009129814550641941</v>
       </c>
       <c r="S4">
         <v>0</v>
@@ -883,55 +883,55 @@
         <v>0</v>
       </c>
       <c r="U4">
-        <v>264.6</v>
+        <v>480.1</v>
       </c>
       <c r="V4">
-        <v>2.354092526690391</v>
+        <v>1.698266713830916</v>
       </c>
       <c r="W4">
-        <v>0.05770403806270586</v>
+        <v>0.1425086399674731</v>
       </c>
       <c r="X4">
-        <v>0.3407847738667649</v>
+        <v>0.195492190388332</v>
       </c>
       <c r="Y4">
-        <v>-0.2830807358040591</v>
+        <v>-0.05298355042085898</v>
       </c>
       <c r="Z4">
-        <v>0.1795891931902295</v>
+        <v>0.6472258628221932</v>
       </c>
       <c r="AA4">
         <v>0</v>
       </c>
       <c r="AB4">
-        <v>0.2167570658256495</v>
+        <v>0.1671033362251388</v>
       </c>
       <c r="AC4">
-        <v>-0.2167570658256495</v>
+        <v>-0.1671033362251388</v>
       </c>
       <c r="AD4">
-        <v>230.5</v>
+        <v>296.5</v>
       </c>
       <c r="AE4">
         <v>0</v>
       </c>
       <c r="AF4">
-        <v>230.5</v>
+        <v>296.5</v>
       </c>
       <c r="AG4">
-        <v>-34.10000000000002</v>
+        <v>-183.6</v>
       </c>
       <c r="AH4">
-        <v>0.6722076407115778</v>
+        <v>0.5119129834254144</v>
       </c>
       <c r="AI4">
-        <v>0.3111921155663561</v>
+        <v>0.3077002905770029</v>
       </c>
       <c r="AJ4">
-        <v>-0.435504469987229</v>
+        <v>-1.852674066599395</v>
       </c>
       <c r="AK4">
-        <v>-0.07162360848561232</v>
+        <v>-0.3797311271975182</v>
       </c>
       <c r="AL4">
         <v>0</v>
@@ -948,7 +948,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Seylan Bank PLC (COSE:SEYB.N0000)</t>
+          <t>Sampath Bank PLC (COSE:SAMP.N0000)</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -957,10 +957,10 @@
         </is>
       </c>
       <c r="D5">
-        <v>0.0275</v>
+        <v>0.109</v>
       </c>
       <c r="E5">
-        <v>-0.0304</v>
+        <v>0.0848</v>
       </c>
       <c r="G5">
         <v>0</v>
@@ -969,34 +969,34 @@
         <v>0</v>
       </c>
       <c r="I5">
-        <v>0</v>
+        <v>0.0006507633984100403</v>
       </c>
       <c r="J5">
-        <v>0</v>
+        <v>0.0004285338507883691</v>
       </c>
       <c r="K5">
-        <v>10.7</v>
+        <v>59.2</v>
       </c>
       <c r="L5">
-        <v>0.1798319327731092</v>
+        <v>0.2648769574944072</v>
       </c>
       <c r="M5">
-        <v>0.001</v>
+        <v>12.8</v>
       </c>
       <c r="N5">
-        <v>2.155172413793104e-05</v>
+        <v>0.05007824726134585</v>
       </c>
       <c r="O5">
-        <v>9.345794392523365e-05</v>
+        <v>0.2162162162162162</v>
       </c>
       <c r="P5">
-        <v>0.001</v>
+        <v>12.8</v>
       </c>
       <c r="Q5">
-        <v>2.155172413793104e-05</v>
+        <v>0.05007824726134585</v>
       </c>
       <c r="R5">
-        <v>9.345794392523365e-05</v>
+        <v>0.2162162162162162</v>
       </c>
       <c r="S5">
         <v>0</v>
@@ -1005,61 +1005,67 @@
         <v>0</v>
       </c>
       <c r="U5">
-        <v>94.7</v>
+        <v>339</v>
       </c>
       <c r="V5">
-        <v>2.040948275862069</v>
+        <v>1.326291079812207</v>
       </c>
       <c r="W5">
-        <v>0.04076190476190476</v>
+        <v>0.1691911974849957</v>
       </c>
       <c r="X5">
-        <v>0.4680835178999435</v>
+        <v>0.1979475107512003</v>
       </c>
       <c r="Y5">
-        <v>-0.4273216131380387</v>
+        <v>-0.02875631326620462</v>
       </c>
       <c r="Z5">
-        <v>0.1221013749230454</v>
+        <v>0.4406999544958401</v>
       </c>
       <c r="AA5">
-        <v>0</v>
+        <v>0.0001888548485423614</v>
       </c>
       <c r="AB5">
-        <v>0.2192501970721273</v>
+        <v>0.1677996391450826</v>
       </c>
       <c r="AC5">
-        <v>-0.2192501970721273</v>
+        <v>-0.1676107842965402</v>
       </c>
       <c r="AD5">
-        <v>161</v>
+        <v>277.4</v>
       </c>
       <c r="AE5">
-        <v>0</v>
+        <v>0.14777190227678</v>
       </c>
       <c r="AF5">
-        <v>161</v>
+        <v>277.5477719022767</v>
       </c>
       <c r="AG5">
-        <v>66.3</v>
+        <v>-61.45222809772326</v>
       </c>
       <c r="AH5">
-        <v>0.7762777242044359</v>
+        <v>0.5205831976226467</v>
       </c>
       <c r="AI5">
-        <v>0.5119236883942766</v>
+        <v>0.369990796877863</v>
       </c>
       <c r="AJ5">
-        <v>0.5882874889086069</v>
+        <v>-0.3165229633881914</v>
       </c>
       <c r="AK5">
-        <v>0.3016378525932666</v>
+        <v>-0.1494650641383738</v>
       </c>
       <c r="AL5">
         <v>0</v>
       </c>
       <c r="AM5">
         <v>0</v>
+      </c>
+      <c r="AN5">
+        <v>1585.142857142857</v>
+      </c>
+      <c r="AP5">
+        <v>-351.1555891298473</v>
       </c>
     </row>
     <row r="6">
@@ -1070,7 +1076,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Union Bank of Colombo PLC (COSE:UBC.N0000)</t>
+          <t>Commercial Bank of Ceylon PLC (COSE:COMB.N0000)</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1079,10 +1085,10 @@
         </is>
       </c>
       <c r="D6">
-        <v>0.0451</v>
+        <v>0.06860000000000001</v>
       </c>
       <c r="E6">
-        <v>-0.0136</v>
+        <v>0.065</v>
       </c>
       <c r="G6">
         <v>0</v>
@@ -1097,82 +1103,85 @@
         <v>0</v>
       </c>
       <c r="K6">
-        <v>1.33</v>
+        <v>71.2</v>
       </c>
       <c r="L6">
-        <v>0.08209876543209878</v>
+        <v>0.3114610673665792</v>
       </c>
       <c r="M6">
-        <v>-0</v>
+        <v>17.0833</v>
       </c>
       <c r="N6">
-        <v>-0</v>
+        <v>0.04444146722164412</v>
       </c>
       <c r="O6">
-        <v>-0</v>
+        <v>0.2399339887640449</v>
       </c>
       <c r="P6">
-        <v>-0</v>
+        <v>17.0833</v>
       </c>
       <c r="Q6">
-        <v>-0</v>
+        <v>0.04444146722164412</v>
       </c>
       <c r="R6">
-        <v>-0</v>
+        <v>0.2399339887640449</v>
       </c>
       <c r="S6">
         <v>0</v>
       </c>
+      <c r="T6">
+        <v>0</v>
+      </c>
       <c r="U6">
-        <v>16.3</v>
+        <v>354.7</v>
       </c>
       <c r="V6">
-        <v>0.8358974358974359</v>
+        <v>0.9227367325702394</v>
       </c>
       <c r="W6">
-        <v>0.01496062992125984</v>
+        <v>0.1297849070360919</v>
       </c>
       <c r="X6">
-        <v>0.4250186123067822</v>
+        <v>0.2359059142476171</v>
       </c>
       <c r="Y6">
-        <v>-0.4100579823855224</v>
+        <v>-0.1061210072115253</v>
       </c>
       <c r="Z6">
-        <v>0.1153846153846154</v>
+        <v>0.2358159686403961</v>
       </c>
       <c r="AA6">
         <v>0</v>
       </c>
       <c r="AB6">
-        <v>0.2214707797408157</v>
+        <v>0.1760949605335747</v>
       </c>
       <c r="AC6">
-        <v>-0.2214707797408157</v>
+        <v>-0.1760949605335747</v>
       </c>
       <c r="AD6">
-        <v>58.3</v>
+        <v>637.6</v>
       </c>
       <c r="AE6">
         <v>0</v>
       </c>
       <c r="AF6">
-        <v>58.3</v>
+        <v>637.6</v>
       </c>
       <c r="AG6">
-        <v>42</v>
+        <v>282.9</v>
       </c>
       <c r="AH6">
-        <v>0.7493573264781491</v>
+        <v>0.6238747553816048</v>
       </c>
       <c r="AI6">
-        <v>0.5295186194368756</v>
+        <v>0.4856054836252856</v>
       </c>
       <c r="AJ6">
-        <v>0.6829268292682927</v>
+        <v>0.4239472501123933</v>
       </c>
       <c r="AK6">
-        <v>0.4477611940298508</v>
+        <v>0.2952102681832412</v>
       </c>
       <c r="AL6">
         <v>0</v>
@@ -1189,7 +1198,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Sampath Bank PLC (COSE:SAMP.N0000)</t>
+          <t>Seylan Bank PLC (COSE:SEYB.N0000)</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1198,10 +1207,10 @@
         </is>
       </c>
       <c r="D7">
-        <v>0.0433</v>
+        <v>0.107</v>
       </c>
       <c r="E7">
-        <v>0.007019999999999999</v>
+        <v>0.105</v>
       </c>
       <c r="G7">
         <v>0</v>
@@ -1210,34 +1219,34 @@
         <v>0</v>
       </c>
       <c r="I7">
-        <v>0.001320784590803098</v>
+        <v>0</v>
       </c>
       <c r="J7">
-        <v>0.0009983395263816843</v>
+        <v>0</v>
       </c>
       <c r="K7">
-        <v>32.2</v>
+        <v>20.3</v>
       </c>
       <c r="L7">
-        <v>0.2511700468018721</v>
+        <v>0.2015888778550149</v>
       </c>
       <c r="M7">
-        <v>13.3</v>
+        <v>0.002</v>
       </c>
       <c r="N7">
-        <v>0.1248826291079812</v>
+        <v>2.72108843537415e-05</v>
       </c>
       <c r="O7">
-        <v>0.4130434782608696</v>
+        <v>9.852216748768472e-05</v>
       </c>
       <c r="P7">
-        <v>13.3</v>
+        <v>0.002</v>
       </c>
       <c r="Q7">
-        <v>0.1248826291079812</v>
+        <v>2.72108843537415e-05</v>
       </c>
       <c r="R7">
-        <v>0.4130434782608696</v>
+        <v>9.852216748768472e-05</v>
       </c>
       <c r="S7">
         <v>0</v>
@@ -1246,67 +1255,61 @@
         <v>0</v>
       </c>
       <c r="U7">
-        <v>135.6</v>
+        <v>216.4</v>
       </c>
       <c r="V7">
-        <v>1.273239436619718</v>
+        <v>2.94421768707483</v>
       </c>
       <c r="W7">
-        <v>0.05270049099836335</v>
+        <v>0.1354236157438292</v>
       </c>
       <c r="X7">
-        <v>0.4035073492462563</v>
+        <v>0.2532038501820424</v>
       </c>
       <c r="Y7">
-        <v>-0.3508068582478929</v>
+        <v>-0.1177802344382132</v>
       </c>
       <c r="Z7">
-        <v>0.1340908276789866</v>
+        <v>0.4657724329324699</v>
       </c>
       <c r="AA7">
-        <v>0.0001338681733971675</v>
+        <v>0</v>
       </c>
       <c r="AB7">
-        <v>0.2222059980723402</v>
+        <v>0.1787955833563059</v>
       </c>
       <c r="AC7">
-        <v>-0.222072129898943</v>
+        <v>-0.1787955833563059</v>
       </c>
       <c r="AD7">
-        <v>292.7</v>
+        <v>141.1</v>
       </c>
       <c r="AE7">
-        <v>0.1683770772952145</v>
+        <v>0</v>
       </c>
       <c r="AF7">
-        <v>292.8683770772952</v>
+        <v>141.1</v>
       </c>
       <c r="AG7">
-        <v>157.2683770772952</v>
+        <v>-75.30000000000001</v>
       </c>
       <c r="AH7">
-        <v>0.7333289110685206</v>
+        <v>0.657502329916123</v>
       </c>
       <c r="AI7">
-        <v>0.4556359452669165</v>
+        <v>0.4199404761904762</v>
       </c>
       <c r="AJ7">
-        <v>0.5962366634693625</v>
+        <v>41.83333333333307</v>
       </c>
       <c r="AK7">
-        <v>0.3100910549344575</v>
+        <v>-0.6295986622073579</v>
       </c>
       <c r="AL7">
         <v>0</v>
       </c>
       <c r="AM7">
         <v>0</v>
-      </c>
-      <c r="AN7">
-        <v>1441.871921182266</v>
-      </c>
-      <c r="AP7">
-        <v>774.7210693462816</v>
       </c>
     </row>
     <row r="8">
@@ -1317,7 +1320,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Nations Trust Bank PLC (COSE:NTB.N0000)</t>
+          <t>Union Bank of Colombo PLC (COSE:UBC.N0000)</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1326,10 +1329,10 @@
         </is>
       </c>
       <c r="D8">
-        <v>0.0898</v>
+        <v>0.0528</v>
       </c>
       <c r="E8">
-        <v>0.163</v>
+        <v>0.005659999999999999</v>
       </c>
       <c r="G8">
         <v>0</v>
@@ -1344,85 +1347,82 @@
         <v>0</v>
       </c>
       <c r="K8">
+        <v>1.77</v>
+      </c>
+      <c r="L8">
+        <v>0.08009049773755655</v>
+      </c>
+      <c r="M8">
+        <v>-0</v>
+      </c>
+      <c r="N8">
+        <v>-0</v>
+      </c>
+      <c r="O8">
+        <v>-0</v>
+      </c>
+      <c r="P8">
+        <v>-0</v>
+      </c>
+      <c r="Q8">
+        <v>-0</v>
+      </c>
+      <c r="R8">
+        <v>-0</v>
+      </c>
+      <c r="S8">
+        <v>0</v>
+      </c>
+      <c r="U8">
         <v>19.1</v>
       </c>
-      <c r="L8">
-        <v>0.305111821086262</v>
-      </c>
-      <c r="M8">
-        <v>2.7135</v>
-      </c>
-      <c r="N8">
-        <v>0.06922193877551019</v>
-      </c>
-      <c r="O8">
-        <v>0.1420680628272251</v>
-      </c>
-      <c r="P8">
-        <v>2.7135</v>
-      </c>
-      <c r="Q8">
-        <v>0.06922193877551019</v>
-      </c>
-      <c r="R8">
-        <v>0.1420680628272251</v>
-      </c>
-      <c r="S8">
-        <v>0</v>
-      </c>
-      <c r="T8">
-        <v>0</v>
-      </c>
-      <c r="U8">
-        <v>139</v>
-      </c>
       <c r="V8">
-        <v>3.545918367346939</v>
+        <v>0.5701492537313433</v>
       </c>
       <c r="W8">
-        <v>0.09891248058001037</v>
+        <v>0.03463796477495108</v>
       </c>
       <c r="X8">
-        <v>0.5197605062720867</v>
+        <v>0.2603034111009942</v>
       </c>
       <c r="Y8">
-        <v>-0.4208480256920764</v>
+        <v>-0.2256654463260431</v>
       </c>
       <c r="Z8">
-        <v>0.1408640864086408</v>
+        <v>0.2373791621911923</v>
       </c>
       <c r="AA8">
         <v>0</v>
       </c>
       <c r="AB8">
-        <v>0.228311947950361</v>
+        <v>0.1797691720194247</v>
       </c>
       <c r="AC8">
-        <v>-0.228311947950361</v>
+        <v>-0.1797691720194247</v>
       </c>
       <c r="AD8">
-        <v>158.6</v>
+        <v>67.90000000000001</v>
       </c>
       <c r="AE8">
         <v>0</v>
       </c>
       <c r="AF8">
-        <v>158.6</v>
+        <v>67.90000000000001</v>
       </c>
       <c r="AG8">
-        <v>19.59999999999999</v>
+        <v>48.8</v>
       </c>
       <c r="AH8">
-        <v>0.8018200202224468</v>
+        <v>0.6696252465483234</v>
       </c>
       <c r="AI8">
-        <v>0.5700934579439252</v>
+        <v>0.5284046692607004</v>
       </c>
       <c r="AJ8">
-        <v>0.3333333333333333</v>
+        <v>0.5929526123936816</v>
       </c>
       <c r="AK8">
-        <v>0.1408045977011494</v>
+        <v>0.4460694698354662</v>
       </c>
       <c r="AL8">
         <v>0</v>
@@ -1439,7 +1439,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Pan Asia Banking Corporation PLC (COSE:PABC.N0000)</t>
+          <t>Nations Trust Bank PLC (COSE:NTB.N0000)</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1448,10 +1448,10 @@
         </is>
       </c>
       <c r="D9">
-        <v>0.0341</v>
+        <v>0.158</v>
       </c>
       <c r="E9">
-        <v>0.0349</v>
+        <v>0.242</v>
       </c>
       <c r="G9">
         <v>0</v>
@@ -1466,82 +1466,85 @@
         <v>0</v>
       </c>
       <c r="K9">
-        <v>4.11</v>
+        <v>35.2</v>
       </c>
       <c r="L9">
-        <v>0.2118556701030928</v>
+        <v>0.3042350907519447</v>
       </c>
       <c r="M9">
-        <v>-0</v>
+        <v>0.5590000000000001</v>
       </c>
       <c r="N9">
-        <v>-0</v>
+        <v>0.005313688212927757</v>
       </c>
       <c r="O9">
-        <v>-0</v>
+        <v>0.01588068181818182</v>
       </c>
       <c r="P9">
-        <v>-0</v>
+        <v>0.5590000000000001</v>
       </c>
       <c r="Q9">
-        <v>-0</v>
+        <v>0.005313688212927757</v>
       </c>
       <c r="R9">
-        <v>-0</v>
+        <v>0.01588068181818182</v>
       </c>
       <c r="S9">
         <v>0</v>
       </c>
+      <c r="T9">
+        <v>0</v>
+      </c>
       <c r="U9">
-        <v>18.5</v>
+        <v>155.7</v>
       </c>
       <c r="V9">
-        <v>1.62280701754386</v>
+        <v>1.480038022813688</v>
       </c>
       <c r="W9">
-        <v>0.04702517162471396</v>
+        <v>0.294314381270903</v>
       </c>
       <c r="X9">
-        <v>0.6171473609251668</v>
+        <v>0.2608537763709873</v>
       </c>
       <c r="Y9">
-        <v>-0.5701221893004528</v>
+        <v>0.03346060489991576</v>
       </c>
       <c r="Z9">
-        <v>0.1252420916720465</v>
+        <v>0.8311781609195403</v>
       </c>
       <c r="AA9">
         <v>0</v>
       </c>
       <c r="AB9">
-        <v>0.2290231958086404</v>
+        <v>0.1798417749646036</v>
       </c>
       <c r="AC9">
-        <v>-0.2290231958086404</v>
+        <v>-0.1798417749646036</v>
       </c>
       <c r="AD9">
-        <v>58.5</v>
+        <v>214.1</v>
       </c>
       <c r="AE9">
         <v>0</v>
       </c>
       <c r="AF9">
-        <v>58.5</v>
+        <v>214.1</v>
       </c>
       <c r="AG9">
-        <v>40</v>
+        <v>58.40000000000001</v>
       </c>
       <c r="AH9">
-        <v>0.8369098712446351</v>
+        <v>0.6705292828061384</v>
       </c>
       <c r="AI9">
-        <v>0.5294117647058824</v>
+        <v>0.5392947103274559</v>
       </c>
       <c r="AJ9">
-        <v>0.7782101167315175</v>
+        <v>0.3569682151589242</v>
       </c>
       <c r="AK9">
-        <v>0.4347826086956522</v>
+        <v>0.2420223787815997</v>
       </c>
       <c r="AL9">
         <v>0</v>
@@ -1558,7 +1561,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Commercial Bank of Ceylon PLC (COSE:COMB.N0000)</t>
+          <t>Pan Asia Banking Corporation PLC (COSE:PABC.N0000)</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1567,10 +1570,10 @@
         </is>
       </c>
       <c r="D10">
-        <v>0.079</v>
+        <v>0.05400000000000001</v>
       </c>
       <c r="E10">
-        <v>0.0473</v>
+        <v>0.126</v>
       </c>
       <c r="G10">
         <v>0</v>
@@ -1585,85 +1588,82 @@
         <v>0</v>
       </c>
       <c r="K10">
-        <v>55.5</v>
+        <v>8.710000000000001</v>
       </c>
       <c r="L10">
-        <v>0.293495505023797</v>
+        <v>0.3237918215613383</v>
       </c>
       <c r="M10">
-        <v>14.6</v>
+        <v>-0</v>
       </c>
       <c r="N10">
-        <v>0.08706022659511033</v>
+        <v>-0</v>
       </c>
       <c r="O10">
-        <v>0.263063063063063</v>
+        <v>-0</v>
       </c>
       <c r="P10">
-        <v>14.6</v>
+        <v>-0</v>
       </c>
       <c r="Q10">
-        <v>0.08706022659511033</v>
+        <v>-0</v>
       </c>
       <c r="R10">
-        <v>0.263063063063063</v>
+        <v>-0</v>
       </c>
       <c r="S10">
         <v>0</v>
       </c>
-      <c r="T10">
-        <v>0</v>
-      </c>
       <c r="U10">
-        <v>320.9</v>
+        <v>21.5</v>
       </c>
       <c r="V10">
-        <v>1.913536076326774</v>
+        <v>0.8237547892720306</v>
       </c>
       <c r="W10">
-        <v>0.06682721252257676</v>
+        <v>0.1675</v>
       </c>
       <c r="X10">
-        <v>0.5535659608408841</v>
+        <v>0.3075242177208526</v>
       </c>
       <c r="Y10">
-        <v>-0.4867387483183073</v>
+        <v>-0.1400242177208526</v>
       </c>
       <c r="Z10">
-        <v>0.09979418438967755</v>
+        <v>0.2923913043478261</v>
       </c>
       <c r="AA10">
         <v>0</v>
       </c>
       <c r="AB10">
-        <v>0.2295397756813018</v>
+        <v>0.1848252118624744</v>
       </c>
       <c r="AC10">
-        <v>-0.2295397756813018</v>
+        <v>-0.1848252118624744</v>
       </c>
       <c r="AD10">
-        <v>741.7</v>
+        <v>71.5</v>
       </c>
       <c r="AE10">
         <v>0</v>
       </c>
       <c r="AF10">
-        <v>741.7</v>
+        <v>71.5</v>
       </c>
       <c r="AG10">
-        <v>420.8000000000001</v>
+        <v>50</v>
       </c>
       <c r="AH10">
-        <v>0.8155926984825159</v>
+        <v>0.7325819672131147</v>
       </c>
       <c r="AI10">
-        <v>0.5700561063715318</v>
+        <v>0.5136494252873564</v>
       </c>
       <c r="AJ10">
-        <v>0.7150382327952423</v>
+        <v>0.6570302233902759</v>
       </c>
       <c r="AK10">
-        <v>0.4293001428279943</v>
+        <v>0.4248088360237893</v>
       </c>
       <c r="AL10">
         <v>0</v>
@@ -1680,7 +1680,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>DFCC Bank PLC (COSE:DFCC.N0000)</t>
+          <t>National Development Bank PLC (COSE:NDB.N0000)</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1689,10 +1689,10 @@
         </is>
       </c>
       <c r="D11">
-        <v>-0.00511</v>
+        <v>0.0805</v>
       </c>
       <c r="E11">
-        <v>-0.189</v>
+        <v>0.123</v>
       </c>
       <c r="G11">
         <v>0</v>
@@ -1707,85 +1707,82 @@
         <v>0</v>
       </c>
       <c r="K11">
-        <v>3.93</v>
+        <v>24.1</v>
       </c>
       <c r="L11">
-        <v>0.1126074498567335</v>
+        <v>0.3027638190954774</v>
       </c>
       <c r="M11">
-        <v>0.245</v>
+        <v>-0</v>
       </c>
       <c r="N11">
-        <v>0.006980056980056979</v>
+        <v>-0</v>
       </c>
       <c r="O11">
-        <v>0.06234096692111959</v>
+        <v>-0</v>
       </c>
       <c r="P11">
-        <v>0.245</v>
+        <v>-0</v>
       </c>
       <c r="Q11">
-        <v>0.006980056980056979</v>
+        <v>-0</v>
       </c>
       <c r="R11">
-        <v>0.06234096692111959</v>
+        <v>-0</v>
       </c>
       <c r="S11">
         <v>0</v>
       </c>
-      <c r="T11">
-        <v>0</v>
-      </c>
       <c r="U11">
-        <v>51.6</v>
+        <v>189.3</v>
       </c>
       <c r="V11">
-        <v>1.47008547008547</v>
+        <v>2.360349127182045</v>
       </c>
       <c r="W11">
-        <v>0.0148694665153235</v>
+        <v>0.1342618384401114</v>
       </c>
       <c r="X11">
-        <v>1.091682059913699</v>
+        <v>0.3128907644220555</v>
       </c>
       <c r="Y11">
-        <v>-1.076812593398375</v>
+        <v>-0.1786289259819441</v>
       </c>
       <c r="Z11">
-        <v>0.04825774336283185</v>
+        <v>0.223784087714366</v>
       </c>
       <c r="AA11">
         <v>0</v>
       </c>
       <c r="AB11">
-        <v>0.2301995034572172</v>
+        <v>0.1852804627012516</v>
       </c>
       <c r="AC11">
-        <v>-0.2301995034572172</v>
+        <v>-0.1852804627012516</v>
       </c>
       <c r="AD11">
-        <v>365.8</v>
+        <v>226.2</v>
       </c>
       <c r="AE11">
         <v>0</v>
       </c>
       <c r="AF11">
-        <v>365.8</v>
+        <v>226.2</v>
       </c>
       <c r="AG11">
-        <v>314.2</v>
+        <v>36.89999999999998</v>
       </c>
       <c r="AH11">
-        <v>0.9124469942629084</v>
+        <v>0.7382506527415144</v>
       </c>
       <c r="AI11">
-        <v>0.7418373555059825</v>
+        <v>0.4854077253218884</v>
       </c>
       <c r="AJ11">
-        <v>0.8995133123389636</v>
+        <v>0.3151152860802731</v>
       </c>
       <c r="AK11">
-        <v>0.7116647791619479</v>
+        <v>0.1333574268160462</v>
       </c>
       <c r="AL11">
         <v>0</v>
@@ -1802,7 +1799,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>National Development Bank PLC (COSE:NDB.N0000)</t>
+          <t>DFCC Bank PLC (COSE:DFCC.N0000)</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1811,10 +1808,10 @@
         </is>
       </c>
       <c r="D12">
-        <v>0.00971</v>
+        <v>0.139</v>
       </c>
       <c r="E12">
-        <v>-0.134</v>
+        <v>0.243</v>
       </c>
       <c r="G12">
         <v>0</v>
@@ -1829,28 +1826,28 @@
         <v>0</v>
       </c>
       <c r="K12">
-        <v>4.32</v>
+        <v>26.8</v>
       </c>
       <c r="L12">
-        <v>0.1046004842615012</v>
+        <v>0.3626522327469553</v>
       </c>
       <c r="M12">
-        <v>0.947</v>
+        <v>0.096</v>
       </c>
       <c r="N12">
-        <v>0.02861027190332326</v>
+        <v>0.0009239653512993262</v>
       </c>
       <c r="O12">
-        <v>0.2192129629629629</v>
+        <v>0.003582089552238806</v>
       </c>
       <c r="P12">
-        <v>0.947</v>
+        <v>0.096</v>
       </c>
       <c r="Q12">
-        <v>0.02861027190332326</v>
+        <v>0.0009239653512993262</v>
       </c>
       <c r="R12">
-        <v>0.2192129629629629</v>
+        <v>0.003582089552238806</v>
       </c>
       <c r="S12">
         <v>0</v>
@@ -1859,55 +1856,55 @@
         <v>0</v>
       </c>
       <c r="U12">
-        <v>81.59999999999999</v>
+        <v>113.4</v>
       </c>
       <c r="V12">
-        <v>2.465256797583081</v>
+        <v>1.091434071222329</v>
       </c>
       <c r="W12">
-        <v>0.01394898288666451</v>
+        <v>0.2123613312202852</v>
       </c>
       <c r="X12">
-        <v>0.855482528996665</v>
+        <v>0.367584121344168</v>
       </c>
       <c r="Y12">
-        <v>-0.8415335461100005</v>
+        <v>-0.1552227901238828</v>
       </c>
       <c r="Z12">
-        <v>0.06294772138393537</v>
+        <v>0.1678019981834696</v>
       </c>
       <c r="AA12">
         <v>0</v>
       </c>
       <c r="AB12">
-        <v>0.2358357376622084</v>
+        <v>0.1890150101406088</v>
       </c>
       <c r="AC12">
-        <v>-0.2358357376622084</v>
+        <v>-0.1890150101406088</v>
       </c>
       <c r="AD12">
-        <v>257.8</v>
+        <v>378.8</v>
       </c>
       <c r="AE12">
         <v>0</v>
       </c>
       <c r="AF12">
-        <v>257.8</v>
+        <v>378.8</v>
       </c>
       <c r="AG12">
-        <v>176.2</v>
+        <v>265.4</v>
       </c>
       <c r="AH12">
-        <v>0.8862151942248194</v>
+        <v>0.7847524342241557</v>
       </c>
       <c r="AI12">
-        <v>0.5844479709816368</v>
+        <v>0.6353572626635356</v>
       </c>
       <c r="AJ12">
-        <v>0.8418537983755375</v>
+        <v>0.718656918494449</v>
       </c>
       <c r="AK12">
-        <v>0.4901251738525731</v>
+        <v>0.5497100248550124</v>
       </c>
       <c r="AL12">
         <v>0</v>
@@ -1933,7 +1930,10 @@
         </is>
       </c>
       <c r="D13">
-        <v>0.0751</v>
+        <v>0.0922</v>
+      </c>
+      <c r="E13">
+        <v>0.00619</v>
       </c>
       <c r="G13">
         <v>0</v>
@@ -1948,85 +1948,82 @@
         <v>0</v>
       </c>
       <c r="K13">
-        <v>-0.392</v>
+        <v>1.61</v>
       </c>
       <c r="L13">
-        <v>-0.02529032258064516</v>
+        <v>0.07252252252252253</v>
       </c>
       <c r="M13">
-        <v>0.796</v>
+        <v>-0</v>
       </c>
       <c r="N13">
-        <v>0.08504273504273505</v>
+        <v>-0</v>
       </c>
       <c r="O13">
-        <v>-2.030612244897959</v>
+        <v>-0</v>
       </c>
       <c r="P13">
-        <v>0.66</v>
+        <v>-0</v>
       </c>
       <c r="Q13">
-        <v>0.07051282051282053</v>
+        <v>-0</v>
       </c>
       <c r="R13">
-        <v>-1.683673469387755</v>
+        <v>-0</v>
       </c>
       <c r="S13">
-        <v>0.136</v>
-      </c>
-      <c r="T13">
-        <v>0.1708542713567839</v>
+        <v>0</v>
       </c>
       <c r="U13">
-        <v>19.1</v>
+        <v>9.57</v>
       </c>
       <c r="V13">
-        <v>2.040598290598291</v>
+        <v>0.6095541401273886</v>
       </c>
       <c r="W13">
-        <v>-0.005584045584045584</v>
+        <v>0.04497206703910615</v>
       </c>
       <c r="X13">
-        <v>1.150653381900702</v>
+        <v>0.5261184193436583</v>
       </c>
       <c r="Y13">
-        <v>-1.156237427484748</v>
+        <v>-0.4811463523045522</v>
       </c>
       <c r="Z13">
-        <v>0.07746126936531735</v>
+        <v>0.1843853820598007</v>
       </c>
       <c r="AA13">
         <v>0</v>
       </c>
       <c r="AB13">
-        <v>0.2359501885375771</v>
+        <v>0.193150728026729</v>
       </c>
       <c r="AC13">
-        <v>-0.2359501885375771</v>
+        <v>-0.193150728026729</v>
       </c>
       <c r="AD13">
-        <v>103.7</v>
+        <v>94.8</v>
       </c>
       <c r="AE13">
         <v>0</v>
       </c>
       <c r="AF13">
-        <v>103.7</v>
+        <v>94.8</v>
       </c>
       <c r="AG13">
-        <v>84.59999999999999</v>
+        <v>85.22999999999999</v>
       </c>
       <c r="AH13">
-        <v>0.9172120997700336</v>
+        <v>0.857918552036199</v>
       </c>
       <c r="AI13">
-        <v>0.7433691756272401</v>
+        <v>0.6884531590413944</v>
       </c>
       <c r="AJ13">
-        <v>0.9003831417624522</v>
+        <v>0.844446646190429</v>
       </c>
       <c r="AK13">
-        <v>0.7026578073089701</v>
+        <v>0.6651837977054553</v>
       </c>
       <c r="AL13">
         <v>0</v>
